--- a/out/牙醫體系_統一出勤表_範本.xlsx
+++ b/out/牙醫體系_統一出勤表_範本.xlsx
@@ -2563,7 +2563,7 @@
       </c>
       <c r="M6" s="18" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>國</t>
         </is>
       </c>
       <c r="N6" s="18" t="inlineStr">
@@ -2733,22 +2733,22 @@
       </c>
       <c r="M7" s="18" t="inlineStr">
         <is>
+          <t>國</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="P7" s="18" t="inlineStr">
+        <is>
           <t>訓</t>
-        </is>
-      </c>
-      <c r="N7" s="18" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="O7" s="18" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="P7" s="18" t="inlineStr">
-        <is>
-          <t>OFF</t>
         </is>
       </c>
       <c r="Q7" s="18" t="inlineStr">
@@ -2863,147 +2863,147 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>支</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
           <t>FD</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>國</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="O8" s="18" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="P8" s="18" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>支</t>
+        </is>
+      </c>
+      <c r="R8" s="18" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="S8" s="18" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="T8" s="18" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="U8" s="18" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="V8" s="18" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="W8" s="18" t="inlineStr">
+        <is>
+          <t>FD</t>
+        </is>
+      </c>
+      <c r="X8" s="18" t="inlineStr">
+        <is>
+          <t>支</t>
+        </is>
+      </c>
+      <c r="Y8" s="18" t="inlineStr">
+        <is>
+          <t>FD</t>
+        </is>
+      </c>
+      <c r="Z8" s="18" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AA8" s="18" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="AB8" s="18" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AC8" s="18" t="inlineStr">
+        <is>
+          <t>FD</t>
+        </is>
+      </c>
+      <c r="AD8" s="18" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="AE8" s="18" t="inlineStr">
+        <is>
+          <t>支</t>
+        </is>
+      </c>
+      <c r="AF8" s="18" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="AG8" s="18" t="inlineStr">
         <is>
           <t>OFF</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>FD</t>
-        </is>
-      </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="M8" s="18" t="inlineStr">
-        <is>
-          <t>FD</t>
-        </is>
-      </c>
-      <c r="N8" s="18" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="O8" s="18" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="P8" s="18" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="Q8" s="18" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="R8" s="18" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="S8" s="18" t="inlineStr">
-        <is>
-          <t>FD</t>
-        </is>
-      </c>
-      <c r="T8" s="18" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="U8" s="18" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V8" s="18" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="W8" s="18" t="inlineStr">
-        <is>
-          <t>FD</t>
-        </is>
-      </c>
-      <c r="X8" s="18" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="Y8" s="18" t="inlineStr">
-        <is>
-          <t>FD</t>
-        </is>
-      </c>
-      <c r="Z8" s="18" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="AA8" s="18" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="AB8" s="18" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AC8" s="18" t="inlineStr">
-        <is>
-          <t>FD</t>
-        </is>
-      </c>
-      <c r="AD8" s="18" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="AE8" s="18" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AF8" s="18" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="AG8" s="18" t="inlineStr">
-        <is>
-          <t>D2</t>
         </is>
       </c>
       <c r="AH8" s="18" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>國</t>
         </is>
       </c>
       <c r="N9" s="18" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>國</t>
         </is>
       </c>
       <c r="N10" s="18" t="inlineStr">
@@ -3413,62 +3413,62 @@
       </c>
       <c r="M11" s="18" t="inlineStr">
         <is>
+          <t>國</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
           <t>P</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="P11" s="18" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="Q11" s="18" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="R11" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S11" s="18" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="T11" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U11" s="18" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="Q11" s="18" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="R11" s="18" t="inlineStr">
+      <c r="V11" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="S11" s="18" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="T11" s="18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U11" s="18" t="inlineStr">
+      <c r="W11" s="18" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="V11" s="18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W11" s="18" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
       <c r="X11" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>事</t>
         </is>
       </c>
       <c r="Y11" s="18" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>國</t>
         </is>
       </c>
       <c r="N12" s="18" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M13" s="18" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>國</t>
         </is>
       </c>
       <c r="N13" s="18" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="M14" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>國</t>
         </is>
       </c>
       <c r="N14" s="18" t="inlineStr">
